--- a/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-3 元素的多樣性　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上6-3 元素的多樣性　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>同元素不同排列形成的物質稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>原子排列不同</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>同素異形體</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>多樣性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>最堅硬的碳同素異形體是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>硬度最高</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>鑽石</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>硬</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>鉛筆芯的主成分是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>石墨</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>立體網狀鍵結</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>軟</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>鑽石和石墨都是什麼元素？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>硬度最高</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>純碳</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>可以導電的碳是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>石墨</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>鑽石能導電嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>立體網狀鍵結</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>絕緣</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>C60球狀碳分子稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>原子排列不同</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>富勒烯</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>新材料</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>決定同素異形體性質的是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>原子排列</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>立體網狀鍵結</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>結構</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>鑽石與石墨的組成元素都是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>立體網狀鍵結</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>導電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>純碳</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>鑽石與石墨性質不同因原子？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>原子排列</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>排列方式不同</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>結構</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-3 元素的多樣性　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上6-3 元素的多樣性　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>石墨柔軟是因為結構？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>層狀易滑動</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>導電</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鑽石(人造)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>層間弱</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>鑽石堅硬是因為結構？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>立體網狀鍵結</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>原子排列</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>緊密</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>石墨能當電池電極因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>硬度最高</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>原子排列</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>自由電子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>鑽石透明石墨灰黑差在？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>原子排列不同</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>單層</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>結構</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>奈米碳管屬碳的什麼？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>同素異形體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>新型</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>石墨烯是幾層碳？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>立體網狀鍵結</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>單層</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>二維</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>鑽石與石墨誰硬？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>鑽石</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>排列方式不同</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>網狀</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>為何兩者都是純物質？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>只含碳一種元素</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>質軟易在紙上留痕</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>易滑寫字、可導電</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>單一元素</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>石墨可做鉛筆芯因為？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>原子排列鍵結方式不同</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>易滑寫字、可導電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>質軟易在紙上留痕</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>只含碳一種元素</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>軟</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>哪種碳同素異形體最堅硬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>同素異形體</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>鑽石</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>硬</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-3 元素的多樣性　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上6-3 元素的多樣性　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何同是碳性質差這麼多？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>只含碳一種元素</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>複合材料/電子</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>原子排列鍵結方式不同</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>結構決定性質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>石墨層狀結構造成哪些性質？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>易滑寫字、可導電</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>前者原子排列不同、後者中子數不同</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>只含碳一種元素</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>鑽石可用於切割因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>硬度最高</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>富勒烯</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>石墨</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>結構緊密</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>若把石墨施高壓可能變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>原子排列</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>鑽石(人造)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>改變排列</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>奈米碳管強度高應用於？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>原子排列鍵結方式不同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>複合材料/電子</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>易滑寫字、可導電</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>高科技</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>同素異形體與同位素差別？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>質軟易在紙上留痕</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>前者原子排列不同、後者中子數不同</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>易滑寫字、可導電</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>原子排列鍵結方式不同</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>概念</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>石墨烯導電優異可用於？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>觸控面板/電子元件</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>只含碳一種元素</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>質軟易在紙上留痕</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>氧氣O₂與臭氧O₃是同素異形體嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>導電</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>同為氧元素</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何石墨能導電而鑽石不能？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>複合材料/電子</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>觸控面板/電子元件</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>易滑寫字、可導電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>石墨有可自由移動電子鑽石沒有</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>由同素異形體說明氧與臭氧關係？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>同為氧元素不同分子形態</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>原子排列鍵結方式不同</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>石墨有可自由移動電子鑽石沒有</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>複合材料/電子</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>同素異形體</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>多樣性</t>
+          <t>多樣性：同一種元素的原子以不同方式排列組合，形成性質不同的物質，這種物質互稱同素異形體</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>硬</t>
+          <t>硬：鑽石中的碳原子以緻密的立體結構緊密排列鍵結，所以是自然界最硬的物質之一</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>軟</t>
+          <t>軟：石墨的碳原子排列成一層層的平面，層與層之間容易滑動剝落，所以摸起來滑、能寫字</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>純碳</t>
+          <t>純碳：鑽石和石墨都只由碳原子組成，只是排列方式不同，屬於碳的同素異形體</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：石墨層狀結構中有可以自由移動的電子，能夠傳導電流</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>絕緣</t>
+          <t>絕緣：鑽石中每個碳原子的電子都被牢牢鍵結固定住，沒有自由電子，所以不導電</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>新材料：由60個碳原子組成像足球一樣中空球狀結構的分子稱為富勒烯，是碳的另一種同素異形體</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構：同素異形體雖然是同一種元素組成，但原子排列方式不同，這正是造成它們性質差異很大的原因</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>純碳</t>
+          <t>純碳：鑽石和石墨都只由碳元素組成，屬於碳的同素異形體</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構：鑽石和石墨雖然都是碳原子組成，但原子排列的立體結構不同，因此表現出截然不同的物理性質</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>層間弱</t>
+          <t>層間弱：石墨是一層層平面結構堆疊而成，層與層之間的作用力很弱，容易互相滑動剝落，所以質地柔軟</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>緊密</t>
+          <t>緊密：鑽石中每個碳原子都和周圍4個碳原子緊密鍵結，形成穩固的立體網狀結構，所以非常堅硬</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>自由電子</t>
+          <t>自由電子：石墨層狀結構中有可以自由移動的電子，具有良好導電性，適合當作電池的電極材料</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構：鑽石和石墨都是碳，但原子排列方式不同，造成對光的作用不同，鑽石結構讓光線能透過而透明，石墨結構則會吸收反射光線而呈灰黑色</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>新型</t>
+          <t>新型：奈米碳管是由碳原子排列成細長管狀結構的新型材料，也屬於碳的同素異形體之一</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>二維</t>
+          <t>二維：石墨烯是由單層碳原子排列成六角網狀結構的二維材料，可以看作是把石墨剝離到只剩一層</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>網狀</t>
+          <t>網狀：鑽石的碳原子以緊密的立體網狀結構鍵結，遠比石墨的層狀結構堅硬</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>單一元素</t>
+          <t>單一元素：鑽石和石墨都只由碳這一種元素組成，符合純物質「只含一種成分」的定義</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>軟</t>
+          <t>軟：石墨是層狀結構，層與層之間容易滑動剝落，質地較軟，摩擦紙面時容易留下痕跡，適合做鉛筆芯</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>硬</t>
+          <t>硬：鑽石中的碳原子以緻密的立體網狀結構緊密鍵結，是自然界中最堅硬的物質之一</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>結構決定性質</t>
+          <t>結構決定性質：鑽石和石墨雖然都由碳原子組成，但碳原子彼此鍵結排列的方式完全不同(立體網狀 vs 層狀)，這種結構上的差異，造成兩者硬度、導電性等性質天差地遠</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：石墨層與層之間容易滑動剝落，因此質地柔軟能在紙上留下痕跡(適合做鉛筆芯)；同時層內有自由電子能導電，因此也能用於電池電極等導電用途</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>結構緊密</t>
+          <t>結構緊密：鑽石是自然界已知最堅硬的物質，硬度極高，能夠切割磨削其他較軟的材料，因此常用於工業切割和鑽頭</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>改變排列</t>
+          <t>改變排列：在極高溫高壓的條件下，石墨的碳原子可以被迫重新排列成鑽石的立體網狀結構，這正是人造鑽石的製造原理之一</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>高科技</t>
+          <t>高科技：奈米碳管的管狀結構強度極高、導電性佳，被應用於複合材料補強、電子元件等許多高科技領域</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>概念</t>
+          <t>概念：同素異形體是指同一元素的原子以不同方式「排列組合」成不同的物質(如鑽石與石墨)；同位素則是指同一元素的原子「中子數不同」，兩者概念層面完全不同，不要混淆</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：石墨烯的單層結構讓電子移動效率極高、導電性極佳，且輕薄透明，很適合用於觸控面板和各種先進電子元件</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>同為氧元素</t>
+          <t>同為氧元素：氧氣分子由2個氧原子組成、臭氧分子由3個氧原子組成，兩者都只由氧這一種元素構成，只是原子數目和排列不同，屬於氧的同素異形體</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：石墨的層狀結構中有可以自由移動的電子，能夠傳導電流；鑽石中每個碳原子的電子都被牢牢鍵結固定住，沒有自由電子，所以不導電</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>同素異形體</t>
+          <t>同素異形體：氧氣(O₂)和臭氧(O₃)都只由氧原子組成，只是每個分子含有的氧原子數目不同，屬於氧的同素異形體</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-3_三種難度測驗卷.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>硬度最高</t>
+          <t>層狀易滑動</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>同素異形體</t>
+          <t>立體網狀鍵結</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>石墨</t>
+          <t>原子排列不同</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>同素異形體</t>
+          <t>碳</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>單層</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>單層</t>
+          <t>同素異形體</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>富勒烯</t>
+          <t>碳</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>碳</t>
+          <t>排列方式不同</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>同素異形體</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>富勒烯</t>
+          <t>原子排列</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>排列方式不同</t>
+          <t>層狀易滑動</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1399,22 +1399,22 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>鑽石</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>導電</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>同素異形體</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>鑽石</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>碳</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>富勒烯</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>原子排列</t>
+          <t>石墨</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>鑽石</t>
+          <t>同素異形體</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>碳</t>
+          <t>立體網狀鍵結</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
